--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/0050-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/0050-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3CAF9E9-1011-4EDD-8B31-0859F9599D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4675BAF2-FF81-4BD3-81A1-CC228B351A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{532CF67D-D6F4-4DB3-8DBC-00B5ED60AF15}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{61AFA87E-26A3-4EED-8322-1E80E16F9DB8}"/>
   </bookViews>
   <sheets>
     <sheet name="0050-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1526,29 +1526,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D87E47-EC82-43C0-8B89-BB990EF12BFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207E0E45-5A4F-4DB0-9574-0C8D5AD4AB8A}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="8.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="8.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="24" width="8.125" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1582,7 +1583,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1618,7 +1619,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1670,7 +1671,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1738,7 +1739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1810,7 +1811,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1884,7 +1885,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -1958,7 +1959,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -2030,7 +2031,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>28</v>
       </c>
@@ -2104,7 +2105,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
@@ -2178,7 +2179,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2023</v>
       </c>
@@ -2250,7 +2251,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
@@ -2324,7 +2325,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>28</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2022</v>
       </c>
@@ -2470,7 +2471,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>28</v>
       </c>
@@ -2544,7 +2545,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>28</v>
       </c>
@@ -2618,7 +2619,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2021</v>
       </c>
@@ -2690,7 +2691,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>28</v>
       </c>
@@ -2764,7 +2765,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>28</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2020</v>
       </c>
@@ -2910,7 +2911,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
@@ -2984,7 +2985,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>28</v>
       </c>
@@ -3058,7 +3059,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2019</v>
       </c>
@@ -3130,7 +3131,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>28</v>
       </c>
@@ -3204,7 +3205,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>28</v>
       </c>
@@ -3278,7 +3279,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2018</v>
       </c>
@@ -3350,7 +3351,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>28</v>
       </c>
@@ -3424,7 +3425,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>28</v>
       </c>
@@ -3498,7 +3499,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2017</v>
       </c>
@@ -3570,7 +3571,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>28</v>
       </c>
@@ -3644,7 +3645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>28</v>
       </c>
@@ -3718,7 +3719,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2016</v>
       </c>
@@ -3790,7 +3791,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>28</v>
       </c>
@@ -3864,7 +3865,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>28</v>
       </c>
@@ -3938,7 +3939,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2014</v>
       </c>
@@ -4010,7 +4011,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2013</v>
       </c>
@@ -4082,7 +4083,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2012</v>
       </c>
@@ -4154,7 +4155,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2011</v>
       </c>
@@ -4226,7 +4227,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2010</v>
       </c>
@@ -4298,7 +4299,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2009</v>
       </c>
@@ -4370,7 +4371,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2008</v>
       </c>
@@ -4442,7 +4443,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2007</v>
       </c>
@@ -4514,7 +4515,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2006</v>
       </c>
@@ -4586,7 +4587,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2005</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>2004</v>
       </c>
@@ -4730,7 +4731,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2003</v>
       </c>
@@ -4802,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>63</v>
       </c>
@@ -4886,6 +4887,5 @@
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>